--- a/Result/profitability/3305.xlsx
+++ b/Result/profitability/3305.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>0.85375</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>13.985</v>
+        <v>14.675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9037500000000001</v>
+        <v>1.10625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.98</v>
+        <v>14.81</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0225</v>
+        <v>1.135</v>
       </c>
       <c r="N4" t="n">
-        <v>14.31</v>
+        <v>15.24875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8862499999999999</v>
+        <v>1.13125</v>
       </c>
       <c r="N5" t="n">
-        <v>14.06625</v>
+        <v>14.72625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0.95125</v>
+        <v>1.06875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.98625</v>
+        <v>14.52125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9974999999999999</v>
+        <v>1.18375</v>
       </c>
       <c r="N7" t="n">
-        <v>14.565</v>
+        <v>15.24125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12875</v>
+        <v>1.1775</v>
       </c>
       <c r="N8" t="n">
-        <v>15.1475</v>
+        <v>15.21375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4196</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3407</v>
+      </c>
+      <c r="E75" t="n">
+        <v>789</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>487</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.61%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-69</v>
+      </c>
+      <c r="J75" t="n">
+        <v>418</v>
+      </c>
+      <c r="K75" t="n">
+        <v>297</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.06125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.40375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2254335260115607</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5300000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02900930487137399</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.280000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3905325443786982</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
